--- a/output/pdf_financials_xlsx/RI.xlsx
+++ b/output/pdf_financials_xlsx/RI.xlsx
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.50622</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.154916</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -3073,7 +3073,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3684,7 +3688,11 @@
           <t>Share-based payment reserve 10 154,916</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.25311</v>
       </c>
@@ -4436,7 +4444,11 @@
           <t>Share-based payment reserve 195,960</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>0.25311</v>
       </c>

--- a/output/pdf_financials_xlsx/RI.xlsx
+++ b/output/pdf_financials_xlsx/RI.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.313335</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.248439</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.316945</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>-0.13913</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.143881</v>
+        <v>-0.173064</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000112</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.351039</v>
+        <v>-0.351151</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.392292</v>
+        <v>-0.3923</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.038288</v>
+        <v>-0.038291</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.351039</v>
+        <v>-0.351151</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.392292</v>
+        <v>-0.3923</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.038288</v>
+        <v>-0.038291</v>
       </c>
     </row>
     <row r="30">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-318.1372460169292</v>
+        <v>-318.2387486179334</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-358.8835320055988</v>
+        <v>-358.890850707627</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-26.61087982429925</v>
+        <v>-26.61296488070002</v>
       </c>
     </row>
     <row r="31">
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.018256</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.017046</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.030375</v>
       </c>
     </row>
     <row r="35">
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.018256</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.017046</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.030375</v>
       </c>
     </row>
     <row r="37">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.031679</v>
+        <v>0.013423</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.037632</v>
+        <v>0.020586</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.043726</v>
+        <v>0.013351</v>
       </c>
     </row>
     <row r="49">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">

--- a/output/pdf_financials_xlsx/RI.xlsx
+++ b/output/pdf_financials_xlsx/RI.xlsx
@@ -7404,7 +7404,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E155" s="5" t="n">
         <v>0.374</v>
       </c>
